--- a/backend/tests/rejected_smoke.xlsx
+++ b/backend/tests/rejected_smoke.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
